--- a/4_outputs/final/Table33.xlsx
+++ b/4_outputs/final/Table33.xlsx
@@ -441,8 +441,8 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
@@ -732,7 +732,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>+0.2^</t>
+          <t>+0.185^</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.093</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.044</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -777,72 +777,72 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+0.2^</t>
+          <t>+0.185^</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+0.2^*</t>
+          <t>+0.199^*</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>+0.2</t>
+          <t>+0.167</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>+0.3^**</t>
+          <t>+0.329^**</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>+0.3^**</t>
+          <t>+0.333^**</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>+0.2</t>
+          <t>+0.170</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>+0.2^**</t>
+          <t>+0.239^**</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>+0.4^***</t>
+          <t>+0.419^***</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>+0.0^**</t>
+          <t>+0.003^**</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>+0.0^**</t>
+          <t>+0.003^**</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>+0.4^***</t>
+          <t>+0.389^***</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>+0.2^</t>
+          <t>+0.185^</t>
         </is>
       </c>
     </row>
@@ -850,19 +850,19 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.095)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.169)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.112)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -871,72 +871,72 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.095)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.188)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.089)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.102)</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.096)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.188)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.099)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.101)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.081)</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.092)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.001)</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.001)</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.081)</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.095)</t>
         </is>
       </c>
     </row>
@@ -948,117 +948,117 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+0.4^**</t>
+          <t>+0.406^**</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0.5^**</t>
+          <t>+0.544^**</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.090</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.065</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.3^</t>
+          <t>-0.313^</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.295</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>+0.5^**</t>
+          <t>+0.464^**</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.076</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.3^</t>
+          <t>-0.336^</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+0.4^**</t>
+          <t>+0.406^**</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+1.2^</t>
+          <t>+1.210^</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+0.4^**</t>
+          <t>+0.393^**</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>+0.4^**</t>
+          <t>+0.427^**</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>+0.4^*</t>
+          <t>+0.428^*</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>+1.2^</t>
+          <t>+1.210^</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>+0.4^**</t>
+          <t>+0.399^**</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>+0.4^**</t>
+          <t>+0.406^**</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>+0.4^**</t>
+          <t>+0.406^**</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>+0.4^**</t>
+          <t>+0.399^**</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>+0.0^*</t>
+          <t>+0.004^*</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>+0.0^*</t>
+          <t>+0.003^*</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>+0.5^***</t>
+          <t>+0.478^***</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>+0.4^**</t>
+          <t>+0.406^**</t>
         </is>
       </c>
     </row>
@@ -1066,117 +1066,117 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.116)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.177)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.182)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.163)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.179)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.182)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.138)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.173)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.179)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.116)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.656)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.114)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.118)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.150)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.656)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.109)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.116)</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.116)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.108)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.002)</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.001)</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.087)</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.116)</t>
         </is>
       </c>
     </row>
@@ -1188,67 +1188,67 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.035</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.017</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.075</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.063</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1258,47 +1258,47 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>+0.4</t>
+          <t>+0.361</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.064</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.067</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.531</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.0^**</t>
+          <t>-0.035^**</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-0.0^**</t>
+          <t>-0.029^**</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>+0.2</t>
+          <t>+0.237</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.070</t>
         </is>
       </c>
     </row>
@@ -1306,113 +1306,113 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.798)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.777)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(1.2)</t>
+          <t>(1.155)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.133)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(0.9)</t>
+          <t>(0.922)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>(0.9)</t>
+          <t>(0.917)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.777)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.133)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>(0.9)</t>
+          <t>(0.917)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.798)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.781)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>(0.9)</t>
+          <t>(0.896)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.794)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.781)</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.118)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.795)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.798)</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.086)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.011)</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.009)</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>(0.9)</t>
+          <t>(0.904)</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.798)</t>
         </is>
       </c>
     </row>
@@ -1424,67 +1424,67 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.097</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.049</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.023</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.097</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.005</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.104</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.087</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1494,47 +1494,47 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.005</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>+2.6^*</t>
+          <t>+2.596^*</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.089</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.092</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>+2.8^*</t>
+          <t>+2.766^*</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.1^***</t>
+          <t>-0.146^***</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.1^***</t>
+          <t>-0.128^***</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.409</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.097</t>
         </is>
       </c>
     </row>
@@ -1542,113 +1542,113 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.146)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.139)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(1.0)</t>
+          <t>(0.999)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(1.0)</t>
+          <t>(0.979)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(1.3)</t>
+          <t>(1.288)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>(1.3)</t>
+          <t>(1.294)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.139)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>(1.0)</t>
+          <t>(0.979)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>(1.3)</t>
+          <t>(1.294)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.146)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.131)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>(1.3)</t>
+          <t>(1.261)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.147)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.131)</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>(1.2)</t>
+          <t>(1.196)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.147)</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.146)</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>(1.2)</t>
+          <t>(1.188)</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.016)</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.013)</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>(2.1)</t>
+          <t>(2.083)</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>(1.1)</t>
+          <t>(1.146)</t>
         </is>
       </c>
     </row>
@@ -1660,62 +1660,62 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.034</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.017</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.008</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.034</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.002</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.036</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1725,52 +1725,52 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.002</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.061</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.627</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>+0.8</t>
+          <t>+0.764</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>+0.1^***</t>
+          <t>+0.107^***</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>+0.1^***</t>
+          <t>+0.085^***</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.020</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.034</t>
         </is>
       </c>
     </row>
@@ -1778,113 +1778,113 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.669)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.662)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.777)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.800)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>(1.0)</t>
+          <t>(0.952)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>(1.0)</t>
+          <t>(0.960)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.662)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.800)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>(1.0)</t>
+          <t>(0.960)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>(0.6)</t>
+          <t>(0.632)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.688)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.678)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.755)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.660)</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.681)</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>(1.0)</t>
+          <t>(1.019)</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.674)</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.802)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.014)</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.010)</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>(1.2)</t>
+          <t>(1.217)</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.669)</t>
         </is>
       </c>
     </row>
@@ -1896,117 +1896,117 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>+0.0^*</t>
+          <t>+0.003^*</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>+0.0^*</t>
+          <t>+0.003^*</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.055</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
     </row>
@@ -2014,117 +2014,117 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.102)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.102)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.100)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.100)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.160)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.160)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.102)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.100)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.160)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.184)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.102)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.102)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.109)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.137)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.184)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.102)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.102)</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.102)</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.102)</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.001)</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.001)</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>(0.3)</t>
+          <t>(0.332)</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.102)</t>
         </is>
       </c>
     </row>
@@ -2136,117 +2136,117 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.001</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.001</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.157</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
     </row>
@@ -2254,117 +2254,117 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.248)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.248)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.193)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.193)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.151)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.151)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.248)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.193)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.151)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>(0.3)</t>
+          <t>(0.279)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.248)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.248)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>(0.3)</t>
+          <t>(0.277)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.232)</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>(0.3)</t>
+          <t>(0.279)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.248)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.248)</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.248)</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.248)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.003)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.002)</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>(0.4)</t>
+          <t>(0.406)</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>(0.2)</t>
+          <t>(0.248)</t>
         </is>
       </c>
     </row>
@@ -2376,47 +2376,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2426,22 +2426,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2451,42 +2451,42 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>+0.6</t>
+          <t>+0.569</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.494</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>+0.0^*</t>
+          <t>+0.012^*</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>+0.0^*</t>
+          <t>+0.010^*</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.821</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
     </row>
@@ -2494,109 +2494,109 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>(0.4)</t>
+          <t>(0.395)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(0.4)</t>
+          <t>(0.395)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(0.5)</t>
+          <t>(0.479)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(0.5)</t>
+          <t>(0.479)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>(0.3)</t>
+          <t>(0.309)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>(0.3)</t>
+          <t>(0.309)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(0.4)</t>
+          <t>(0.395)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>(0.5)</t>
+          <t>(0.479)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>(0.3)</t>
+          <t>(0.309)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>(0.4)</t>
+          <t>(0.395)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>(0.4)</t>
+          <t>(0.395)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>(0.4)</t>
+          <t>(0.395)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>(0.6)</t>
+          <t>(0.564)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>(0.4)</t>
+          <t>(0.395)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>(0.4)</t>
+          <t>(0.395)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>(0.5)</t>
+          <t>(0.512)</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>(0.5)</t>
+          <t>(0.537)</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.004)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.004)</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>(0.9)</t>
+          <t>(0.878)</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>(0.4)</t>
+          <t>(0.395)</t>
         </is>
       </c>
     </row>
@@ -2608,47 +2608,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2683,42 +2683,42 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>+0.8</t>
+          <t>+0.778</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>+0.7</t>
+          <t>+0.703</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.003</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.003</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.787</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.000</t>
         </is>
       </c>
     </row>
@@ -2726,105 +2726,105 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.723)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.723)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(1.3)</t>
+          <t>(1.302)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(1.3)</t>
+          <t>(1.302)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.823)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.823)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.723)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>(1.3)</t>
+          <t>(1.302)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.823)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.723)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.729)</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>(1.0)</t>
+          <t>(0.980)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.723)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.723)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>(0.9)</t>
+          <t>(0.896)</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>(0.9)</t>
+          <t>(0.910)</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.008)</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.006)</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>(1.3)</t>
+          <t>(1.283)</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>(0.7)</t>
+          <t>(0.723)</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.141</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.041</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2955,19 +2955,19 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.097)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.104)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.063)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -3026,17 +3026,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.141</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.041</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3120,17 +3120,17 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.097)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.104)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.063)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+7.5^</t>
+          <t>+7.546^</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>+7.5^</t>
+          <t>+7.546^</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3284,7 +3284,7 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>(3.9)</t>
+          <t>(3.860)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -3292,7 +3292,7 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>(3.9)</t>
+          <t>(3.860)</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.821</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.821</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3440,7 +3440,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>(4.3)</t>
+          <t>(4.283)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -3448,7 +3448,7 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>(4.3)</t>
+          <t>(4.283)</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+7.3</t>
+          <t>+7.301</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>+7.3</t>
+          <t>+7.301</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3596,7 +3596,7 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>(4.5)</t>
+          <t>(4.472)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3604,7 +3604,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>(4.5)</t>
+          <t>(4.472)</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>+1.540</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3752,7 +3752,7 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>(3.6)</t>
+          <t>(3.615)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -3760,7 +3760,7 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>(3.6)</t>
+          <t>(3.615)</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+4.8</t>
+          <t>+4.778</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>+4.8</t>
+          <t>+4.778</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3908,7 +3908,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>(3.7)</t>
+          <t>(3.667)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3916,7 +3916,7 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>(3.7)</t>
+          <t>(3.667)</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr"/>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.994</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.994</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4064,7 +4064,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>(4.6)</t>
+          <t>(4.599)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -4072,7 +4072,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>(4.6)</t>
+          <t>(4.599)</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr"/>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+1.6</t>
+          <t>+1.634</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>+1.6</t>
+          <t>+1.634</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4220,7 +4220,7 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>(4.4)</t>
+          <t>(4.377)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -4228,7 +4228,7 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>(4.4)</t>
+          <t>(4.377)</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>+2.005</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>+2.005</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4376,7 +4376,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>(4.2)</t>
+          <t>(4.178)</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -4384,7 +4384,7 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>(4.2)</t>
+          <t>(4.178)</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>+1.453</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>+1.453</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4532,7 +4532,7 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>(4.1)</t>
+          <t>(4.148)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -4540,7 +4540,7 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>(4.1)</t>
+          <t>(4.148)</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr"/>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+10.1^</t>
+          <t>+10.103^</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>+10.1^</t>
+          <t>+10.103^</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4688,7 +4688,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>(5.2)</t>
+          <t>(5.245)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -4696,7 +4696,7 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>(5.2)</t>
+          <t>(5.245)</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr"/>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+1.9</t>
+          <t>+1.950</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>+1.9</t>
+          <t>+1.950</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4844,7 +4844,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>(3.6)</t>
+          <t>(3.570)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -4852,7 +4852,7 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>(3.6)</t>
+          <t>(3.570)</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr"/>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>+3.523</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>+3.523</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -5000,7 +5000,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>(4.7)</t>
+          <t>(4.729)</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -5008,7 +5008,7 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>(4.7)</t>
+          <t>(4.729)</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-1.6^</t>
+          <t>-1.594^</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>-1.6^</t>
+          <t>-1.594^</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -5156,7 +5156,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.760)</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -5164,7 +5164,7 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>(0.8)</t>
+          <t>(0.760)</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr"/>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>+0.8</t>
+          <t>+0.809</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>+0.8</t>
+          <t>+0.809</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -5312,7 +5312,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>(4.6)</t>
+          <t>(4.588)</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -5320,7 +5320,7 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>(4.6)</t>
+          <t>(4.588)</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr"/>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.840</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.840</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5468,7 +5468,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>(4.4)</t>
+          <t>(4.395)</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -5476,7 +5476,7 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>(4.4)</t>
+          <t>(4.395)</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-9.4</t>
+          <t>-9.426</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>-9.4</t>
+          <t>-9.426</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5624,7 +5624,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>(5.7)</t>
+          <t>(5.690)</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -5632,7 +5632,7 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>(5.7)</t>
+          <t>(5.690)</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.045</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.075</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -5785,14 +5785,14 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.091)</t>
         </is>
       </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.096)</t>
         </is>
       </c>
       <c r="U59" t="inlineStr"/>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>-0.5^***</t>
+          <t>-0.452^***</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>-0.5^***</t>
+          <t>-0.482^***</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -5941,14 +5941,14 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.095)</t>
         </is>
       </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.102)</t>
         </is>
       </c>
       <c r="U61" t="inlineStr"/>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+0.103</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>-0.1^</t>
+          <t>-0.145^</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -6098,13 +6098,13 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.076)</t>
         </is>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.075)</t>
         </is>
       </c>
       <c r="U63" t="inlineStr"/>
@@ -6205,12 +6205,12 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>-0.1^</t>
+          <t>-0.101^</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>-0.1^</t>
+          <t>-0.087^</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -6255,12 +6255,12 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.048)</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>(0.0)</t>
+          <t>(0.047)</t>
         </is>
       </c>
       <c r="U65" t="inlineStr"/>
@@ -6361,12 +6361,12 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.138</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.124</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -6411,12 +6411,12 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.104)</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>(0.1)</t>
+          <t>(0.103)</t>
         </is>
       </c>
       <c r="U67" t="inlineStr"/>
